--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M1B1_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M1B1_IN_Piura.xlsx
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>0.56</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>12.7</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C13" s="29">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>66.08</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>20.61</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>188.7969</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>1.1704</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>0.62</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1965,11 +1965,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>187.6265</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>99.38</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>188.8831</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2286,6 +2286,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2463,6 +2464,7 @@
       <c r="F14" s="17" t="inlineStr"/>
       <c r="G14" s="17" t="inlineStr"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -2507,6 +2509,7 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="156" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
@@ -2693,11 +2696,11 @@
       </c>
       <c r="B11" s="31">
         <f>SUM(B10:B10)</f>
-        <v/>
+        <v>188.8</v>
       </c>
       <c r="C11" s="23">
         <f>SUM(C10:C10)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -2707,19 +2710,19 @@
       <c r="E11" s="17" t="inlineStr"/>
       <c r="F11" s="17">
         <f>ROUND(AVERAGE(F10:F10),2)</f>
-        <v/>
+        <v>18.7</v>
       </c>
       <c r="G11" s="22">
         <f>ROUND(AVERAGE(G10:G10),4)</f>
-        <v/>
+        <v>0.3193</v>
       </c>
       <c r="H11" s="23">
         <f>ROUND(AVERAGE(H10:H10),2)</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="I11" s="23">
         <f>ROUND(AVERAGE(I10:I10),2)</f>
-        <v/>
+        <v>99.38</v>
       </c>
     </row>
     <row r="12"/>
